--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/KANSAS_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/KANSAS_2011.xlsx
@@ -679,7 +679,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="19">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C103">
@@ -2515,7 +2515,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="121">
@@ -2569,7 +2569,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="124">
@@ -2659,7 +2659,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="129">
@@ -2695,7 +2695,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="131">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C154">
@@ -3253,7 +3253,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="162">
@@ -3451,7 +3451,7 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="173">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C187">
@@ -3829,7 +3829,7 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="194">
@@ -4117,7 +4117,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="210">
@@ -4495,7 +4495,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="231">
@@ -4765,7 +4765,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="246">
@@ -4819,7 +4819,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="249">
@@ -5233,7 +5233,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="272">
@@ -5449,7 +5449,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="284">
@@ -5881,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="308">
@@ -6547,7 +6547,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="345">
@@ -6799,7 +6799,7 @@
         <v>7</v>
       </c>
       <c r="D358">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="359">
@@ -7807,7 +7807,7 @@
         <v>7</v>
       </c>
       <c r="D414">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="415">
@@ -8185,7 +8185,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="436">
@@ -8671,7 +8671,7 @@
         <v>7</v>
       </c>
       <c r="D462">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="463">
@@ -8761,7 +8761,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="468">
@@ -9643,7 +9643,7 @@
         <v>7</v>
       </c>
       <c r="D516">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="517">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C533">
@@ -9985,7 +9985,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="536">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C577">
@@ -12217,7 +12217,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="660">
@@ -12685,7 +12685,7 @@
         <v>7</v>
       </c>
       <c r="D685">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="686">
@@ -13063,7 +13063,7 @@
         <v>7</v>
       </c>
       <c r="D706">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="707">
@@ -15612,7 +15612,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C848">
@@ -16051,7 +16051,7 @@
         <v>7</v>
       </c>
       <c r="D872">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="873">
@@ -16393,7 +16393,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="892">
@@ -16465,7 +16465,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>0.000927029532512</v>
+        <v>0.0009270295325120002</v>
       </c>
     </row>
     <row r="896">
